--- a/baselines/openvas/OpenVAS_JuiceShop.xlsx
+++ b/baselines/openvas/OpenVAS_JuiceShop.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,92 +429,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>detection_result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>detection_method</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>solution</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>insight</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>product_detection_result</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>log_method</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>cvss</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>port</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>protocol</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>references</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>plugin</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>plugin_details</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>instances</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -910,10 +922,10 @@
 - No 404 check (OID: 1.3.6.1.4.1.25623.1.0.10386)
 - Web mirroring / webmirror.nasl (OID: 1.3.6.1.4.1.25623.1.0.10662)
 - Directory Scanner / DDI_Directory_Scanner.nasl (OID: 1.3.6.1.4.1.25623.1.0.11032)
-- The con_x001C_gured 'cgi_path' within the 'Scanner Preferences' of the scan con_x001C_g in use
-- The con_x001C_gured 'Enable CGI scanning', 'Enable generic web application scanning' and 'Add
+- The configured 'cgi_path' within the 'Scanner Preferences' of the scan config in use
+- The configured 'Enable CGI scanning', 'Enable generic web application scanning' and 'Add
 historic /scripts and /cgi-bin to directories for CGI scanning' within the 'Global variable settings'
-of the scan con_x001C_g in use
+of the scan config in use
 If you think any of this information is wrong please report it to the referenced community portal.</t>
         </is>
       </c>
@@ -1075,7 +1087,7 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>All known security headers are being checked on the host. On completion a report will hand
-back whether a speci_x001C_c security header has been implemented (including its value) or is missing
+back whether a specific security header has been implemented (including its value) or is missing
 on the target.</t>
         </is>
       </c>
@@ -1745,7 +1757,7 @@
           <t>This routine reports all SSL/TLS cipher suites accepted by a service.
 As the NVT 'SSL/TLS: Check Supported Cipher Suites' (OID: 1.3.6.1.4.1.25623.1.0.900234)
 might run into a timeout the actual reporting of all accepted cipher suites takes place in this
-NVT instead. The script preference 'Report timeout' allows you to con_x001C_gure if such an timeout
+NVT instead. The script preference 'Report timeout' allows you to configure if such an timeout
 is reported.</t>
         </is>
       </c>
@@ -1830,7 +1842,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>This plugin uses wapiti to _x001C_nd web security issues.
+          <t>This plugin uses wapiti to find web security issues.
 Make sure to have wapiti 2.x as wapiti 1.x is not supported.
 See the preferences section for wapiti options.
 Note that the scanner is using limited set of wapiti options. Therefore, for more complete web
@@ -1900,7 +1912,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Postx SMTP Server Detection</t>
+          <t>Postfix SMTP Server Detection</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2386,7 +2398,7 @@
       <c r="B27" t="inlineStr">
         <is>
           <t>This plugin performs service detection.
-This plugin is a complement of _x001C_nd_service.nasl. It sends a '&lt;xml/&gt;' request to the remaining
+This plugin is a complement of find_service.nasl. It sends a '&lt;xml/&gt;' request to the remaining
 unknown services and tries to identify them.</t>
         </is>
       </c>
@@ -2791,7 +2803,7 @@
           <t>This routine reports all SSL/TLS cipher suites accepted by a service.
 As the NVT 'SSL/TLS: Check Supported Cipher Suites' (OID: 1.3.6.1.4.1.25623.1.0.900234)
 might run into a timeout the actual reporting of all accepted cipher suites takes place in this
-NVT instead. The script preference 'Report timeout' allows you to con_x001C_gure if such an timeout
+NVT instead. The script preference 'Report timeout' allows you to configure if such an timeout
 is reported.</t>
         </is>
       </c>
@@ -2968,7 +2980,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>This script consolidates the OS information detected by several NVTs and tries to _x001C_nd the best
+          <t>This script consolidates the OS information detected by several NVTs and tries to find the best
 matching OS.
 Furthermore it reports all previously collected information leading to this best matching OS. It
 also reports possible additional information which might help to improve the OS detection.
